--- a/sales_order_forms/006_promotional_floor_decal_order_form--sales_order_forms.xlsx
+++ b/sales_order_forms/006_promotional_floor_decal_order_form--sales_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'vinyl_sticker'}</t>
+          <t>vinyl_sticker</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Vinyl Sticker'}</t>
+          <t>Vinyl Sticker</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'vinyl_decal'}</t>
+          <t>vinyl_decal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Vinyl Decal'}</t>
+          <t>Vinyl Decal</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'magnetic_decal'}</t>
+          <t>magnetic_decal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Magnetic Decal'}</t>
+          <t>Magnetic Decal</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'printed_decal'}</t>
+          <t>printed_decal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Printed Decal'}</t>
+          <t>Printed Decal</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'yellow'}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Yellow'}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'2in_x_2in'}</t>
+          <t>2in_x_2in</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '2in x 2in'}</t>
+          <t>2in x 2in</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'4in_x_4in'}</t>
+          <t>4in_x_4in</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '4in x 4in'}</t>
+          <t>4in x 4in</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'6in_x_6in'}</t>
+          <t>6in_x_6in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '6in x 6in'}</t>
+          <t>6in x 6in</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'8in_x_8in'}</t>
+          <t>8in_x_8in</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '8in x 8in'}</t>
+          <t>8in x 8in</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'vinyl_decal'}</t>
+          <t>vinyl_decal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Vinyl Decal'}</t>
+          <t>Vinyl Decal</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'magnetic_decal'}</t>
+          <t>magnetic_decal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Magnetic Decal'}</t>
+          <t>Magnetic Decal</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'printed_decal'}</t>
+          <t>printed_decal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Printed Decal'}</t>
+          <t>Printed Decal</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'6in_x_6in'}</t>
+          <t>6in_x_6in</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '6in x 6in'}</t>
+          <t>6in x 6in</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'8in_x_8in'}</t>
+          <t>8in_x_8in</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': '8in x 8in'}</t>
+          <t>8in x 8in</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'10in_x_10in'}</t>
+          <t>10in_x_10in</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': '10in x 10in'}</t>
+          <t>10in x 10in</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'12in_x_12in'}</t>
+          <t>12in_x_12in</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': '12in x 12in'}</t>
+          <t>12in x 12in</t>
         </is>
       </c>
     </row>
